--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -10272,7 +10272,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -19124,7 +19124,7 @@
           <t>B | 390呎 (2房)
 $781万
 $20,025/呎
-(26年-05月)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,36 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5764,7 +5637,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -10276,10 +10149,10 @@
         </is>
       </c>
       <c r="H211" s="5" t="n">
-        <v>7809600</v>
+        <v>8238700</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>20025</v>
+        <v>21125</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
@@ -15102,14 +14975,14 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
-        <v>7717100</v>
+        <v>7551100</v>
       </c>
       <c r="I316" s="5" t="n">
-        <v>19787</v>
+        <v>19362</v>
       </c>
       <c r="J316" s="3" t="inlineStr">
         <is>
@@ -17272,3241 +17145,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:P29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>首岸第1期 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>360 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>338 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>10 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$861万
-$22,085/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$847万
-$21,830/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$841万
-$21,620/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$841万
-$21,400/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$860万
-$21,541/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$830万
-$20,857/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$824万
-$20,652/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$756万
-$22,315/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K6" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$764万
-$22,540/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$780万
-$23,017/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M6" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$740万
-$21,818/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N6" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$726万
-$21,427/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O6" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$721万
-$21,017/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P6" s="16" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,400万
-$21,805/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$857万
-$21,968/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$841万
-$21,678/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$835万
-$21,463/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$853万
-$21,714/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$835万
-$20,930/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$820万
-$20,614/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$814万
-$20,410/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$745万
-$21,969/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K7" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$747万
-$22,033/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$770万
-$22,707/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M7" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$729万
-$21,510/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N7" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$720万
-$21,225/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O7" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$714万
-$20,829/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P7" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$927万
-$21,321/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,387万
-$21,600/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$852万
-$21,858/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$853万
-$21,984/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$849万
-$21,828/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$829万
-$21,085/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$827万
-$20,722/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$812万
-$20,411/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$803万
-$20,129/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$735万
-$21,681/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K8" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$776万
-$22,904/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$747万
-$22,033/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M8" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$722万
-$21,303/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N8" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$713万
-$21,024/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O8" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$709万
-$20,670/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P8" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$919万
-$21,135/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,377万
-$21,444/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$848万
-$21,749/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$827万
-$21,324/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$827万
-$21,271/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$825万
-$20,997/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$818万
-$20,508/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$802万
-$20,159/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$795万
-$19,922/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$725万
-$21,378/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K9" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$726万
-$21,408/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$740万
-$21,827/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$731万
-$21,563/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$722万
-$21,286/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O9" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$720万
-$20,986/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P9" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$912万
-$20,955/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,367万
-$21,296/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$844万
-$21,637/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$821万
-$21,153/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$823万
-$21,161/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$819万
-$20,828/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$856万
-$21,462/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$796万
-$19,997/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$788万
-$19,758/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$733万
-$21,623/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$715万
-$21,086/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$732万
-$21,582/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$725万
-$21,398/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$698万
-$20,594/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$735万
-$21,439/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P10" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$905万
-$20,809/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,359万
-$21,165/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$838万
-$21,483/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$860万
-$22,176/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$864万
-$22,223/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$857万
-$21,794/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$852万
-$21,348/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$789万
-$19,835/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$799万
-$20,031/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$713万
-$21,024/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K11" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$709万
-$20,917/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$766万
-$22,606/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M11" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$722万
-$21,286/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$694万
-$20,468/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$688万
-$20,065/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P11" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$898万
-$20,639/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,350万
-$21,035/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$849万
-$21,778/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$811万
-$20,909/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$814万
-$20,914/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$809万
-$20,592/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$845万
-$21,180/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$779万
-$19,581/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$775万
-$19,420/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$709万
-$20,914/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K12" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$747万
-$22,029/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$762万
-$22,488/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$742万
-$21,876/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$705万
-$20,808/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$686万
-$19,999/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P12" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$891万
-$20,489/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,340万
-$20,866/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$825万
-$21,142/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$806万
-$20,777/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$852万
-$21,905/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$802万
-$20,416/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$795万
-$19,931/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$769万
-$19,327/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$811万
-$20,336/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$703万
-$20,745/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K13" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$704万
-$20,771/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$718万
-$21,185/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M13" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$738万
-$21,757/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$686万
-$20,251/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O13" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$684万
-$19,927/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P13" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$888万
-$20,420/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,345万
-$20,945/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$818万
-$20,972/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$799万
-$20,597/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$845万
-$21,712/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$796万
-$20,242/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$786万
-$19,696/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$741万
-$18,621/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$805万
-$20,172/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$735万
-$21,686/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K14" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$695万
-$20,503/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$715万
-$21,091/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$734万
-$21,641/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$699万
-$20,605/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$719万
-$20,952/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P14" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$885万
-$20,348/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,320万
-$20,567/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$810万
-$20,778/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$792万
-$20,419/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$810万
-$20,835/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$798万
-$20,306/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$779万
-$19,518/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$738万
-$18,554/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$800万
-$20,043/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$690万
-$20,369/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$686万
-$20,240/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$712万
-$20,997/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$729万
-$21,505/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$681万
-$20,076/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$676万
-$19,701/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P15" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$882万
-$20,277/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,301万
-$20,270/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$802万
-$20,564/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$786万
-$20,245/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$803万
-$20,637/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$774万
-$19,707/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$772万
-$19,338/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$736万
-$18,490/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$797万
-$19,975/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$683万
-$20,146/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$677万
-$19,974/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$704万
-$20,771/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$726万
-$21,409/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$675万
-$19,912/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O16" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$673万
-$19,633/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P16" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$879万
-$20,208/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,251万
-$19,491/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$796万
-$20,403/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$799万
-$20,585/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$778万
-$19,999/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$763万
-$19,422/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$766万
-$19,187/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$732万
-$18,396/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$793万
-$19,870/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$689万
-$20,331/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$712万
-$21,009/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$699万
-$20,608/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$700万
-$20,635/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$666万
-$19,660/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O17" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$668万
-$19,476/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P17" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$876万
-$20,143/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,231万
-$19,178/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$832万
-$21,336/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$776万
-$20,001/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$788万
-$20,250/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$751万
-$19,105/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$797万
-$19,963/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$727万
-$18,264/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$791万
-$19,827/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$686万
-$20,249/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$687万
-$20,273/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L18" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$693万
-$20,452/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M18" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$719万
-$21,216/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N18" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$661万
-$19,486/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O18" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$662万
-$19,301/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P18" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$921万
-$21,166/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,215万
-$18,927/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$781万
-$20,025/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$771万
-$19,877/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$808万
-$20,769/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$738万
-$18,788/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$745万
-$18,674/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$764万
-$19,200/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$788万
-$19,759/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$669万
-$19,741/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$670万
-$19,765/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L19" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$689万
-$20,323/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M19" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$713万
-$21,038/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N19" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$658万
-$19,416/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O19" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$660万
-$19,237/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P19" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$870万
-$19,993/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,211万
-$18,860/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$777万
-$19,917/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$768万
-$19,788/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$762万
-$19,580/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$761万
-$19,368/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$776万
-$19,443/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$722万
-$18,136/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$786万
-$19,687/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$667万
-$19,671/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$704万
-$20,777/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L20" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$722万
-$21,301/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M20" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$709万
-$20,905/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N20" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$656万
-$19,349/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O20" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$658万
-$19,171/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P20" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$867万
-$19,924/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,207万
-$18,794/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$790万
-$20,245/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$761万
-$19,621/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$799万
-$20,545/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$708万
-$18,024/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$718万
-$18,004/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$759万
-$19,062/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$783万
-$19,619/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$664万
-$19,596/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$665万
-$19,623/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L21" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$680万
-$20,063/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M21" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$668万
-$19,706/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N21" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$654万
-$19,282/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O21" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$655万
-$19,102/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P21" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$864万
-$19,853/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,229万
-$19,137/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$786万
-$20,155/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$757万
-$19,516/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$752万
-$19,330/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$706万
-$17,961/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$716万
-$17,940/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$717万
-$18,006/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$781万
-$19,564/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$662万
-$19,526/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$676万
-$19,944/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L22" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$676万
-$19,953/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M22" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$666万
-$19,636/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N22" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$653万
-$19,250/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O22" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$654万
-$19,078/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P22" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$861万
-$19,783/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,198万
-$18,661/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$765万
-$19,612/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$796万
-$20,514/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$749万
-$19,243/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$703万
-$17,894/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$713万
-$17,876/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$730万
-$18,336/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$779万
-$19,531/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$660万
-$19,456/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$656万
-$19,365/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L23" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$685万
-$20,196/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="M23" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$663万
-$19,563/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N23" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$651万
-$19,201/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O23" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$653万
-$19,028/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P23" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$905万
-$20,793/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,194万
-$18,594/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$802万
-$20,576/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$793万
-$20,439/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$746万
-$19,171/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$701万
-$17,830/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$750万
-$18,791/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$711万
-$17,875/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$778万
-$19,501/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$693万
-$20,449/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$690万
-$20,353/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L24" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$664万
-$19,596/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M24" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$661万
-$19,494/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N24" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$650万
-$19,172/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O24" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$652万
-$18,999/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P24" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$854万
-$19,639/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,218万
-$18,965/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$758万
-$19,429/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$789万
-$20,338/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$758万
-$19,496/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$699万
-$17,792/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$709万
-$17,776/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$710万
-$17,841/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$776万
-$19,441/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$670万
-$19,768/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$667万
-$19,675/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L25" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$660万
-$19,464/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M25" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$659万
-$19,453/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N25" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$646万
-$19,064/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O25" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$651万
-$18,969/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P25" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$899万
-$20,668/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,187万
-$18,495/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$772万
-$19,787/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$746万
-$19,215/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$756万
-$19,432/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$698万
-$17,765/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$708万
-$17,748/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$709万
-$17,811/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$772万
-$19,358/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$688万
-$20,301/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$649万
-$19,153/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L26" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$656万
-$19,365/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M26" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$656万
-$19,349/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N26" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$645万
-$19,035/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O26" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$647万
-$18,863/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P26" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$848万
-$19,497/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,185万
-$18,461/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$752万
-$19,292/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$741万
-$19,089/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$735万
-$18,888/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$697万
-$17,734/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$707万
-$17,719/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$746万
-$18,756/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$698万
-$17,481/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$650万
-$19,169/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$661万
-$19,500/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L27" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$654万
-$19,292/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M27" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$654万
-$19,279/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N27" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$643万
-$18,968/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O27" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$645万
-$18,797/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P27" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$864万
-$19,853/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1,183万
-$18,427/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$751万
-$19,255/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$778万
-$20,041/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$730万
-$18,764/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$696万
-$17,700/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$706万
-$17,684/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$703万
-$17,660/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$693万
-$17,365/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$678万
-$19,996/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$641万
-$18,919/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L28" s="17" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$648万
-$19,129/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M28" s="17" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$648万
-$19,115/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N28" s="17" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$673万
-$19,854/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O28" s="17" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$657万
-$19,142/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P28" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$842万
-$19,355/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 605呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 352呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 352呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 355呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 362呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 360呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>H | 361呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>J | 301呎 (2房)
-$714万
-$23,708/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
-        <is>
-          <t>K | 301呎 (2房)
-$715万
-$23,742/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L29" s="17" t="inlineStr">
-        <is>
-          <t>L | 301呎 (2房)
-$705万
-$23,424/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>M | 301呎 (2房)
-$690万
-$22,907/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N29" s="17" t="inlineStr">
-        <is>
-          <t>N | 301呎 (2房)
-$687万
-$22,822/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O29" s="17" t="inlineStr">
-        <is>
-          <t>P | 306呎 (2房)
-$701万
-$22,922/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P29" s="17" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$912万
-$20,956/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,95 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +141,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +216,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +643,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -17145,4 +17314,3241 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$861万
+$22,085/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$847万
+$21,830/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$841万
+$21,620/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$841万
+$21,400/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$860万
+$21,541/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$830万
+$20,857/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$824万
+$20,652/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$756万
+$22,315/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$764万
+$22,540/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$780万
+$23,017/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M5" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$740万
+$21,818/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$726万
+$21,427/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O5" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$721万
+$21,017/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P5" s="20" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1400万
+$21,805/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$857万
+$21,968/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$841万
+$21,678/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$835万
+$21,463/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$853万
+$21,714/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$835万
+$20,930/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$820万
+$20,614/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$814万
+$20,410/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$745万
+$21,969/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$747万
+$22,033/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$770万
+$22,707/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M6" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$729万
+$21,510/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$720万
+$21,225/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$714万
+$20,829/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$927万
+$21,321/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1387万
+$21,600/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$852万
+$21,858/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$853万
+$21,984/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$849万
+$21,828/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$829万
+$21,085/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$827万
+$20,722/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$812万
+$20,411/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$803万
+$20,129/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$735万
+$21,681/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$776万
+$22,904/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$747万
+$22,033/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$722万
+$21,303/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$713万
+$21,024/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O7" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$709万
+$20,670/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$919万
+$21,135/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1377万
+$21,444/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$848万
+$21,749/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$827万
+$21,324/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$827万
+$21,271/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$825万
+$20,997/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$818万
+$20,508/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$802万
+$20,159/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$795万
+$19,922/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$725万
+$21,378/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$726万
+$21,408/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$740万
+$21,827/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$731万
+$21,563/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$722万
+$21,286/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O8" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$720万
+$20,986/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$912万
+$20,955/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1367万
+$21,296/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$844万
+$21,637/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$821万
+$21,153/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$823万
+$21,161/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$819万
+$20,828/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$856万
+$21,462/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$796万
+$19,997/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$788万
+$19,758/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$733万
+$21,623/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$715万
+$21,086/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$732万
+$21,582/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M9" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$725万
+$21,398/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$698万
+$20,594/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O9" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$735万
+$21,439/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$905万
+$20,809/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1359万
+$21,165/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$838万
+$21,483/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$860万
+$22,176/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$864万
+$22,223/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$857万
+$21,794/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$852万
+$21,348/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$789万
+$19,835/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$799万
+$20,031/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$713万
+$21,024/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$709万
+$20,917/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$766万
+$22,606/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$722万
+$21,286/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$694万
+$20,468/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O10" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$688万
+$20,065/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$898万
+$20,639/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1350万
+$21,035/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$849万
+$21,778/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$811万
+$20,909/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$814万
+$20,914/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$809万
+$20,592/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$845万
+$21,180/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$779万
+$19,581/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$775万
+$19,420/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$709万
+$20,914/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$747万
+$22,029/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$762万
+$22,488/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M11" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$742万
+$21,876/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$705万
+$20,808/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O11" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$686万
+$19,999/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$891万
+$20,489/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1340万
+$20,866/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$825万
+$21,142/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$806万
+$20,777/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$852万
+$21,905/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$802万
+$20,416/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$795万
+$19,931/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$769万
+$19,327/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$811万
+$20,336/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$703万
+$20,745/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$704万
+$20,771/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$718万
+$21,185/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$738万
+$21,757/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$686万
+$20,251/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$684万
+$19,927/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$888万
+$20,420/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1345万
+$20,945/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$818万
+$20,972/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$799万
+$20,597/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$845万
+$21,712/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$796万
+$20,242/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$786万
+$19,696/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$741万
+$18,621/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$805万
+$20,172/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$735万
+$21,686/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$695万
+$20,503/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$715万
+$21,091/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M13" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$734万
+$21,641/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$699万
+$20,605/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O13" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$719万
+$20,952/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$885万
+$20,348/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1320万
+$20,567/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$810万
+$20,778/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$792万
+$20,419/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$810万
+$20,835/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$798万
+$20,306/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$779万
+$19,518/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$738万
+$18,554/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$800万
+$20,043/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$690万
+$20,369/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$686万
+$20,240/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$712万
+$20,997/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$729万
+$21,505/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$681万
+$20,076/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O14" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$676万
+$19,701/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P14" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$882万
+$20,277/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1301万
+$20,270/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$802万
+$20,564/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$786万
+$20,245/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$803万
+$20,637/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$774万
+$19,707/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$772万
+$19,338/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$736万
+$18,490/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$797万
+$19,975/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$683万
+$20,146/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$677万
+$19,974/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$704万
+$20,771/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$726万
+$21,409/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$675万
+$19,912/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O15" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$673万
+$19,633/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P15" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$879万
+$20,208/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1251万
+$19,491/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$796万
+$20,403/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$799万
+$20,585/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$778万
+$19,999/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$763万
+$19,422/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$766万
+$19,187/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$732万
+$18,396/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$793万
+$19,870/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$689万
+$20,331/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$712万
+$21,009/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$699万
+$20,608/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$700万
+$20,635/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N16" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$666万
+$19,660/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O16" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$668万
+$19,476/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P16" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$876万
+$20,143/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1231万
+$19,178/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$832万
+$21,336/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$776万
+$20,001/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$788万
+$20,250/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$751万
+$19,105/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$797万
+$19,963/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$727万
+$18,264/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$791万
+$19,827/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$686万
+$20,249/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$687万
+$20,273/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$693万
+$20,452/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$719万
+$21,216/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N17" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$661万
+$19,486/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O17" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$662万
+$19,301/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P17" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$921万
+$21,166/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1215万
+$18,927/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$824万
+$21,125/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$771万
+$19,877/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$808万
+$20,769/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$738万
+$18,788/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$745万
+$18,674/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$764万
+$19,200/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$788万
+$19,759/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$669万
+$19,741/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$670万
+$19,765/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$689万
+$20,323/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M18" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$713万
+$21,038/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N18" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$658万
+$19,416/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O18" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$660万
+$19,237/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P18" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$870万
+$19,993/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1211万
+$18,860/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$777万
+$19,917/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$768万
+$19,788/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$762万
+$19,580/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$761万
+$19,368/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$776万
+$19,443/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$722万
+$18,136/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$786万
+$19,687/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$667万
+$19,671/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$704万
+$20,777/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$722万
+$21,301/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M19" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$709万
+$20,905/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N19" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$656万
+$19,349/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O19" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$658万
+$19,171/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P19" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$867万
+$19,924/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1207万
+$18,794/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$790万
+$20,245/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$761万
+$19,621/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$799万
+$20,545/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$708万
+$18,024/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$718万
+$18,004/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$759万
+$19,062/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$783万
+$19,619/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$664万
+$19,596/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$665万
+$19,623/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$680万
+$20,063/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$668万
+$19,706/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N20" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$654万
+$19,282/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O20" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$655万
+$19,102/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P20" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$864万
+$19,853/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1229万
+$19,137/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$786万
+$20,155/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$757万
+$19,516/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$752万
+$19,330/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$706万
+$17,961/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$716万
+$17,940/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$717万
+$18,006/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$781万
+$19,564/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$662万
+$19,526/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$676万
+$19,944/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$676万
+$19,953/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M21" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$666万
+$19,636/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N21" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$653万
+$19,250/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O21" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$654万
+$19,078/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P21" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$861万
+$19,783/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1198万
+$18,661/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$765万
+$19,612/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$796万
+$20,514/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$749万
+$19,243/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$703万
+$17,894/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$713万
+$17,876/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$730万
+$18,336/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$779万
+$19,531/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$660万
+$19,456/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$656万
+$19,365/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$685万
+$20,196/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$663万
+$19,563/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N22" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$651万
+$19,201/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O22" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$653万
+$19,028/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P22" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$905万
+$20,793/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1194万
+$18,594/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$802万
+$20,576/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$793万
+$20,439/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$746万
+$19,171/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$701万
+$17,830/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$750万
+$18,791/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$711万
+$17,875/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$778万
+$19,501/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$693万
+$20,449/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$690万
+$20,353/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L23" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$664万
+$19,596/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M23" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$661万
+$19,494/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N23" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$650万
+$19,172/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O23" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$652万
+$18,999/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P23" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$854万
+$19,639/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1218万
+$18,965/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$758万
+$19,429/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$789万
+$20,338/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$758万
+$19,496/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$699万
+$17,792/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$709万
+$17,776/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$710万
+$17,841/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$776万
+$19,441/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$670万
+$19,768/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$667万
+$19,675/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$660万
+$19,464/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M24" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$659万
+$19,453/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N24" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$646万
+$19,064/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$651万
+$18,969/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P24" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$899万
+$20,668/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1187万
+$18,495/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$755万
+$19,362/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$746万
+$19,215/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$756万
+$19,432/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$698万
+$17,765/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$708万
+$17,748/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$709万
+$17,811/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$772万
+$19,358/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$688万
+$20,301/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$649万
+$19,153/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$656万
+$19,365/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$656万
+$19,349/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N25" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$645万
+$19,035/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O25" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$647万
+$18,863/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P25" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$848万
+$19,497/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1185万
+$18,461/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$752万
+$19,292/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$741万
+$19,089/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$735万
+$18,888/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$697万
+$17,734/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$707万
+$17,719/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$746万
+$18,756/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$698万
+$17,481/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$650万
+$19,169/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$661万
+$19,500/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$654万
+$19,292/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$654万
+$19,279/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N26" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$643万
+$18,968/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O26" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$645万
+$18,797/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P26" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$864万
+$19,853/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1183万
+$18,427/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$751万
+$19,255/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$778万
+$20,041/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$730万
+$18,764/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$696万
+$17,700/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$706万
+$17,684/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$703万
+$17,660/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$693万
+$17,365/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$678万
+$19,996/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$641万
+$18,919/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$648万
+$19,129/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M27" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$648万
+$19,115/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N27" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$673万
+$19,854/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O27" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$657万
+$19,142/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P27" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$842万
+$19,355/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 605呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 352呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 352呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 355呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 362呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 360呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>H | 361呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>J | 301呎 (2房)
+$714万
+$23,708/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>K | 301呎 (2房)
+$715万
+$23,742/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>L | 301呎 (2房)
+$705万
+$23,424/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr">
+        <is>
+          <t>M | 301呎 (2房)
+$690万
+$22,907/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N28" s="21" t="inlineStr">
+        <is>
+          <t>N | 301呎 (2房)
+$687万
+$22,822/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O28" s="21" t="inlineStr">
+        <is>
+          <t>P | 306呎 (2房)
+$701万
+$22,922/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P28" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$912万
+$20,956/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -643,7 +643,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -648,7 +648,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -648,7 +648,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -23339,7 +23339,7 @@
           <t>B | 390呎 (2房)
 $861万
 $22,085/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -23347,7 +23347,7 @@
           <t>C | 388呎 (2房)
 $847万
 $21,830/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -23355,7 +23355,7 @@
           <t>D | 389呎 (2房)
 $841万
 $21,620/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -23363,7 +23363,7 @@
           <t>E | 393呎 (2房)
 $841万
 $21,400/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -23371,7 +23371,7 @@
           <t>F | 399呎 (2房)
 $860万
 $21,541/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -23379,7 +23379,7 @@
           <t>G | 398呎 (2房)
 $830万
 $20,857/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I5" s="21" t="inlineStr">
@@ -23387,7 +23387,7 @@
           <t>H | 399呎 (2房)
 $824万
 $20,652/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -23395,7 +23395,7 @@
           <t>J | 339呎 (2房)
 $756万
 $22,315/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K5" s="21" t="inlineStr">
@@ -23403,7 +23403,7 @@
           <t>K | 339呎 (2房)
 $764万
 $22,540/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
@@ -23411,7 +23411,7 @@
           <t>L | 339呎 (2房)
 $780万
 $23,017/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M5" s="21" t="inlineStr">
@@ -23419,7 +23419,7 @@
           <t>M | 339呎 (2房)
 $740万
 $21,818/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N5" s="21" t="inlineStr">
@@ -23427,7 +23427,7 @@
           <t>N | 339呎 (2房)
 $726万
 $21,427/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O5" s="21" t="inlineStr">
@@ -23435,7 +23435,7 @@
           <t>P | 343呎 (2房)
 $721万
 $21,017/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P5" s="20" t="inlineStr">
@@ -23458,7 +23458,7 @@
           <t>A | 642呎 (3房)
 $1400万
 $21,805/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -23466,7 +23466,7 @@
           <t>B | 390呎 (2房)
 $857万
 $21,968/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -23474,7 +23474,7 @@
           <t>C | 388呎 (2房)
 $841万
 $21,678/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -23482,7 +23482,7 @@
           <t>D | 389呎 (2房)
 $835万
 $21,463/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -23490,7 +23490,7 @@
           <t>E | 393呎 (2房)
 $853万
 $21,714/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -23498,7 +23498,7 @@
           <t>F | 399呎 (2房)
 $835万
 $20,930/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -23506,7 +23506,7 @@
           <t>G | 398呎 (2房)
 $820万
 $20,614/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -23514,7 +23514,7 @@
           <t>H | 399呎 (2房)
 $814万
 $20,410/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -23522,7 +23522,7 @@
           <t>J | 339呎 (2房)
 $745万
 $21,969/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -23530,7 +23530,7 @@
           <t>K | 339呎 (2房)
 $747万
 $22,033/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -23538,7 +23538,7 @@
           <t>L | 339呎 (2房)
 $770万
 $22,707/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -23546,7 +23546,7 @@
           <t>M | 339呎 (2房)
 $729万
 $21,510/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
@@ -23554,7 +23554,7 @@
           <t>N | 339呎 (2房)
 $720万
 $21,225/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O6" s="21" t="inlineStr">
@@ -23562,7 +23562,7 @@
           <t>P | 343呎 (2房)
 $714万
 $20,829/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P6" s="21" t="inlineStr">
@@ -23570,7 +23570,7 @@
           <t>Q | 435呎 (2房)
 $927万
 $21,321/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -23585,7 +23585,7 @@
           <t>A | 642呎 (3房)
 $1387万
 $21,600/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -23593,7 +23593,7 @@
           <t>B | 390呎 (2房)
 $852万
 $21,858/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -23601,7 +23601,7 @@
           <t>C | 388呎 (2房)
 $853万
 $21,984/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -23609,7 +23609,7 @@
           <t>D | 389呎 (2房)
 $849万
 $21,828/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -23617,7 +23617,7 @@
           <t>E | 393呎 (2房)
 $829万
 $21,085/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -23625,7 +23625,7 @@
           <t>F | 399呎 (2房)
 $827万
 $20,722/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -23633,7 +23633,7 @@
           <t>G | 398呎 (2房)
 $812万
 $20,411/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -23641,7 +23641,7 @@
           <t>H | 399呎 (2房)
 $803万
 $20,129/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -23649,7 +23649,7 @@
           <t>J | 339呎 (2房)
 $735万
 $21,681/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -23657,7 +23657,7 @@
           <t>K | 339呎 (2房)
 $776万
 $22,904/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -23665,7 +23665,7 @@
           <t>L | 339呎 (2房)
 $747万
 $22,033/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M7" s="21" t="inlineStr">
@@ -23673,7 +23673,7 @@
           <t>M | 339呎 (2房)
 $722万
 $21,303/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
@@ -23681,7 +23681,7 @@
           <t>N | 339呎 (2房)
 $713万
 $21,024/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -23689,7 +23689,7 @@
           <t>P | 343呎 (2房)
 $709万
 $20,670/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P7" s="21" t="inlineStr">
@@ -23697,7 +23697,7 @@
           <t>Q | 435呎 (2房)
 $919万
 $21,135/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -23712,7 +23712,7 @@
           <t>A | 642呎 (3房)
 $1377万
 $21,444/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -23720,7 +23720,7 @@
           <t>B | 390呎 (2房)
 $848万
 $21,749/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -23728,7 +23728,7 @@
           <t>C | 388呎 (2房)
 $827万
 $21,324/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -23736,7 +23736,7 @@
           <t>D | 389呎 (2房)
 $827万
 $21,271/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -23744,7 +23744,7 @@
           <t>E | 393呎 (2房)
 $825万
 $20,997/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -23752,7 +23752,7 @@
           <t>F | 399呎 (2房)
 $818万
 $20,508/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -23760,7 +23760,7 @@
           <t>G | 398呎 (2房)
 $802万
 $20,159/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -23768,7 +23768,7 @@
           <t>H | 399呎 (2房)
 $795万
 $19,922/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -23776,7 +23776,7 @@
           <t>J | 339呎 (2房)
 $725万
 $21,378/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -23784,7 +23784,7 @@
           <t>K | 339呎 (2房)
 $726万
 $21,408/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -23792,7 +23792,7 @@
           <t>L | 339呎 (2房)
 $740万
 $21,827/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -23800,7 +23800,7 @@
           <t>M | 339呎 (2房)
 $731万
 $21,563/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
@@ -23808,7 +23808,7 @@
           <t>N | 339呎 (2房)
 $722万
 $21,286/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O8" s="21" t="inlineStr">
@@ -23816,7 +23816,7 @@
           <t>P | 343呎 (2房)
 $720万
 $20,986/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P8" s="21" t="inlineStr">
@@ -23824,7 +23824,7 @@
           <t>Q | 435呎 (2房)
 $912万
 $20,955/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -23839,7 +23839,7 @@
           <t>A | 642呎 (3房)
 $1367万
 $21,296/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -23847,7 +23847,7 @@
           <t>B | 390呎 (2房)
 $844万
 $21,637/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -23855,7 +23855,7 @@
           <t>C | 388呎 (2房)
 $821万
 $21,153/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -23863,7 +23863,7 @@
           <t>D | 389呎 (2房)
 $823万
 $21,161/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -23871,7 +23871,7 @@
           <t>E | 393呎 (2房)
 $819万
 $20,828/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -23879,7 +23879,7 @@
           <t>F | 399呎 (2房)
 $856万
 $21,462/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -23887,7 +23887,7 @@
           <t>G | 398呎 (2房)
 $796万
 $19,997/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -23895,7 +23895,7 @@
           <t>H | 399呎 (2房)
 $788万
 $19,758/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -23903,7 +23903,7 @@
           <t>J | 339呎 (2房)
 $733万
 $21,623/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -23911,7 +23911,7 @@
           <t>K | 339呎 (2房)
 $715万
 $21,086/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -23919,7 +23919,7 @@
           <t>L | 339呎 (2房)
 $732万
 $21,582/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
@@ -23927,7 +23927,7 @@
           <t>M | 339呎 (2房)
 $725万
 $21,398/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -23935,7 +23935,7 @@
           <t>N | 339呎 (2房)
 $698万
 $20,594/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O9" s="21" t="inlineStr">
@@ -23943,7 +23943,7 @@
           <t>P | 343呎 (2房)
 $735万
 $21,439/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P9" s="21" t="inlineStr">
@@ -23951,7 +23951,7 @@
           <t>Q | 435呎 (2房)
 $905万
 $20,809/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -23966,7 +23966,7 @@
           <t>A | 642呎 (3房)
 $1359万
 $21,165/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -23974,7 +23974,7 @@
           <t>B | 390呎 (2房)
 $838万
 $21,483/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -23982,7 +23982,7 @@
           <t>C | 388呎 (2房)
 $860万
 $22,176/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -23990,7 +23990,7 @@
           <t>D | 389呎 (2房)
 $864万
 $22,223/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -23998,7 +23998,7 @@
           <t>E | 393呎 (2房)
 $857万
 $21,794/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -24006,7 +24006,7 @@
           <t>F | 399呎 (2房)
 $852万
 $21,348/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -24014,7 +24014,7 @@
           <t>G | 398呎 (2房)
 $789万
 $19,835/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -24022,7 +24022,7 @@
           <t>H | 399呎 (2房)
 $799万
 $20,031/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -24030,7 +24030,7 @@
           <t>J | 339呎 (2房)
 $713万
 $21,024/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -24038,7 +24038,7 @@
           <t>K | 339呎 (2房)
 $709万
 $20,917/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -24046,7 +24046,7 @@
           <t>L | 339呎 (2房)
 $766万
 $22,606/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -24054,7 +24054,7 @@
           <t>M | 339呎 (2房)
 $722万
 $21,286/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -24062,7 +24062,7 @@
           <t>N | 339呎 (2房)
 $694万
 $20,468/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O10" s="21" t="inlineStr">
@@ -24070,7 +24070,7 @@
           <t>P | 343呎 (2房)
 $688万
 $20,065/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P10" s="21" t="inlineStr">
@@ -24078,7 +24078,7 @@
           <t>Q | 435呎 (2房)
 $898万
 $20,639/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -24093,7 +24093,7 @@
           <t>A | 642呎 (3房)
 $1350万
 $21,035/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -24101,7 +24101,7 @@
           <t>B | 390呎 (2房)
 $849万
 $21,778/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -24109,7 +24109,7 @@
           <t>C | 388呎 (2房)
 $811万
 $20,909/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -24117,7 +24117,7 @@
           <t>D | 389呎 (2房)
 $814万
 $20,914/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -24125,7 +24125,7 @@
           <t>E | 393呎 (2房)
 $809万
 $20,592/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -24133,7 +24133,7 @@
           <t>F | 399呎 (2房)
 $845万
 $21,180/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -24141,7 +24141,7 @@
           <t>G | 398呎 (2房)
 $779万
 $19,581/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -24149,7 +24149,7 @@
           <t>H | 399呎 (2房)
 $775万
 $19,420/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -24157,7 +24157,7 @@
           <t>J | 339呎 (2房)
 $709万
 $20,914/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -24165,7 +24165,7 @@
           <t>K | 339呎 (2房)
 $747万
 $22,029/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -24173,7 +24173,7 @@
           <t>L | 339呎 (2房)
 $762万
 $22,488/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
@@ -24181,7 +24181,7 @@
           <t>M | 339呎 (2房)
 $742万
 $21,876/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -24189,7 +24189,7 @@
           <t>N | 339呎 (2房)
 $705万
 $20,808/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O11" s="21" t="inlineStr">
@@ -24197,7 +24197,7 @@
           <t>P | 343呎 (2房)
 $686万
 $19,999/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P11" s="21" t="inlineStr">
@@ -24205,7 +24205,7 @@
           <t>Q | 435呎 (2房)
 $891万
 $20,489/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
           <t>A | 642呎 (3房)
 $1340万
 $20,866/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -24228,7 +24228,7 @@
           <t>B | 390呎 (2房)
 $825万
 $21,142/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -24236,7 +24236,7 @@
           <t>C | 388呎 (2房)
 $806万
 $20,777/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -24244,7 +24244,7 @@
           <t>D | 389呎 (2房)
 $852万
 $21,905/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -24252,7 +24252,7 @@
           <t>E | 393呎 (2房)
 $802万
 $20,416/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -24260,7 +24260,7 @@
           <t>F | 399呎 (2房)
 $795万
 $19,931/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -24268,7 +24268,7 @@
           <t>G | 398呎 (2房)
 $769万
 $19,327/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -24276,7 +24276,7 @@
           <t>H | 399呎 (2房)
 $811万
 $20,336/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -24284,7 +24284,7 @@
           <t>J | 339呎 (2房)
 $703万
 $20,745/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -24292,7 +24292,7 @@
           <t>K | 339呎 (2房)
 $704万
 $20,771/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -24300,7 +24300,7 @@
           <t>L | 339呎 (2房)
 $718万
 $21,185/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
@@ -24308,7 +24308,7 @@
           <t>M | 339呎 (2房)
 $738万
 $21,757/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -24316,7 +24316,7 @@
           <t>N | 339呎 (2房)
 $686万
 $20,251/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O12" s="21" t="inlineStr">
@@ -24324,7 +24324,7 @@
           <t>P | 343呎 (2房)
 $684万
 $19,927/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P12" s="21" t="inlineStr">
@@ -24332,7 +24332,7 @@
           <t>Q | 435呎 (2房)
 $888万
 $20,420/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -24347,7 +24347,7 @@
           <t>A | 642呎 (3房)
 $1345万
 $20,945/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -24355,7 +24355,7 @@
           <t>B | 390呎 (2房)
 $818万
 $20,972/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -24363,7 +24363,7 @@
           <t>C | 388呎 (2房)
 $799万
 $20,597/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -24371,7 +24371,7 @@
           <t>D | 389呎 (2房)
 $845万
 $21,712/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -24379,7 +24379,7 @@
           <t>E | 393呎 (2房)
 $796万
 $20,242/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -24387,7 +24387,7 @@
           <t>F | 399呎 (2房)
 $786万
 $19,696/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -24395,7 +24395,7 @@
           <t>G | 398呎 (2房)
 $741万
 $18,621/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -24403,7 +24403,7 @@
           <t>H | 399呎 (2房)
 $805万
 $20,172/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -24411,7 +24411,7 @@
           <t>J | 339呎 (2房)
 $735万
 $21,686/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -24419,7 +24419,7 @@
           <t>K | 339呎 (2房)
 $695万
 $20,503/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -24427,7 +24427,7 @@
           <t>L | 339呎 (2房)
 $715万
 $21,091/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
@@ -24435,7 +24435,7 @@
           <t>M | 339呎 (2房)
 $734万
 $21,641/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -24443,7 +24443,7 @@
           <t>N | 339呎 (2房)
 $699万
 $20,605/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O13" s="21" t="inlineStr">
@@ -24451,7 +24451,7 @@
           <t>P | 343呎 (2房)
 $719万
 $20,952/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P13" s="21" t="inlineStr">
@@ -24459,7 +24459,7 @@
           <t>Q | 435呎 (2房)
 $885万
 $20,348/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -24474,7 +24474,7 @@
           <t>A | 642呎 (3房)
 $1320万
 $20,567/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -24482,7 +24482,7 @@
           <t>B | 390呎 (2房)
 $810万
 $20,778/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -24490,7 +24490,7 @@
           <t>C | 388呎 (2房)
 $792万
 $20,419/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -24498,7 +24498,7 @@
           <t>D | 389呎 (2房)
 $810万
 $20,835/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -24506,7 +24506,7 @@
           <t>E | 393呎 (2房)
 $798万
 $20,306/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -24514,7 +24514,7 @@
           <t>F | 399呎 (2房)
 $779万
 $19,518/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -24522,7 +24522,7 @@
           <t>G | 398呎 (2房)
 $738万
 $18,554/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -24538,7 +24538,7 @@
           <t>J | 339呎 (2房)
 $690万
 $20,369/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -24546,7 +24546,7 @@
           <t>K | 339呎 (2房)
 $686万
 $20,240/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -24554,7 +24554,7 @@
           <t>L | 339呎 (2房)
 $712万
 $20,997/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -24562,7 +24562,7 @@
           <t>M | 339呎 (2房)
 $729万
 $21,505/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -24570,7 +24570,7 @@
           <t>N | 339呎 (2房)
 $681万
 $20,076/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O14" s="21" t="inlineStr">
@@ -24578,7 +24578,7 @@
           <t>P | 343呎 (2房)
 $676万
 $19,701/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P14" s="21" t="inlineStr">
@@ -24586,7 +24586,7 @@
           <t>Q | 435呎 (2房)
 $882万
 $20,277/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -24601,7 +24601,7 @@
           <t>A | 642呎 (3房)
 $1301万
 $20,270/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -24609,7 +24609,7 @@
           <t>B | 390呎 (2房)
 $802万
 $20,564/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -24617,7 +24617,7 @@
           <t>C | 388呎 (2房)
 $786万
 $20,245/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -24625,7 +24625,7 @@
           <t>D | 389呎 (2房)
 $803万
 $20,637/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -24633,7 +24633,7 @@
           <t>E | 393呎 (2房)
 $774万
 $19,707/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -24641,7 +24641,7 @@
           <t>F | 399呎 (2房)
 $772万
 $19,338/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -24649,7 +24649,7 @@
           <t>G | 398呎 (2房)
 $736万
 $18,490/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -24665,7 +24665,7 @@
           <t>J | 339呎 (2房)
 $683万
 $20,146/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -24673,7 +24673,7 @@
           <t>K | 339呎 (2房)
 $677万
 $19,974/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -24681,7 +24681,7 @@
           <t>L | 339呎 (2房)
 $704万
 $20,771/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr">
@@ -24689,7 +24689,7 @@
           <t>M | 339呎 (2房)
 $726万
 $21,409/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -24697,7 +24697,7 @@
           <t>N | 339呎 (2房)
 $675万
 $19,912/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O15" s="21" t="inlineStr">
@@ -24705,7 +24705,7 @@
           <t>P | 343呎 (2房)
 $673万
 $19,633/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P15" s="21" t="inlineStr">
@@ -24713,7 +24713,7 @@
           <t>Q | 435呎 (2房)
 $879万
 $20,208/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -24728,7 +24728,7 @@
           <t>A | 642呎 (3房)
 $1251万
 $19,491/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -24736,7 +24736,7 @@
           <t>B | 390呎 (2房)
 $796万
 $20,403/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -24744,7 +24744,7 @@
           <t>C | 388呎 (2房)
 $799万
 $20,585/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -24752,7 +24752,7 @@
           <t>D | 389呎 (2房)
 $778万
 $19,999/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -24760,7 +24760,7 @@
           <t>E | 393呎 (2房)
 $763万
 $19,422/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -24768,7 +24768,7 @@
           <t>F | 399呎 (2房)
 $766万
 $19,187/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -24776,7 +24776,7 @@
           <t>G | 398呎 (2房)
 $732万
 $18,396/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -24792,7 +24792,7 @@
           <t>J | 339呎 (2房)
 $689万
 $20,331/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -24800,7 +24800,7 @@
           <t>K | 339呎 (2房)
 $712万
 $21,009/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -24808,7 +24808,7 @@
           <t>L | 339呎 (2房)
 $699万
 $20,608/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -24816,7 +24816,7 @@
           <t>M | 339呎 (2房)
 $700万
 $20,635/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N16" s="21" t="inlineStr">
@@ -24824,7 +24824,7 @@
           <t>N | 339呎 (2房)
 $666万
 $19,660/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O16" s="21" t="inlineStr">
@@ -24832,7 +24832,7 @@
           <t>P | 343呎 (2房)
 $668万
 $19,476/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P16" s="21" t="inlineStr">
@@ -24840,7 +24840,7 @@
           <t>Q | 435呎 (2房)
 $876万
 $20,143/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -24855,7 +24855,7 @@
           <t>A | 642呎 (3房)
 $1231万
 $19,178/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -24863,7 +24863,7 @@
           <t>B | 390呎 (2房)
 $832万
 $21,336/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -24871,7 +24871,7 @@
           <t>C | 388呎 (2房)
 $776万
 $20,001/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -24879,7 +24879,7 @@
           <t>D | 389呎 (2房)
 $788万
 $20,250/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -24887,7 +24887,7 @@
           <t>E | 393呎 (2房)
 $751万
 $19,105/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -24895,7 +24895,7 @@
           <t>F | 399呎 (2房)
 $797万
 $19,963/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -24903,7 +24903,7 @@
           <t>G | 398呎 (2房)
 $727万
 $18,264/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -24919,7 +24919,7 @@
           <t>J | 339呎 (2房)
 $686万
 $20,249/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -24927,7 +24927,7 @@
           <t>K | 339呎 (2房)
 $687万
 $20,273/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -24935,7 +24935,7 @@
           <t>L | 339呎 (2房)
 $693万
 $20,452/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
@@ -24943,7 +24943,7 @@
           <t>M | 339呎 (2房)
 $719万
 $21,216/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
@@ -24951,7 +24951,7 @@
           <t>N | 339呎 (2房)
 $661万
 $19,486/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O17" s="21" t="inlineStr">
@@ -24959,7 +24959,7 @@
           <t>P | 343呎 (2房)
 $662万
 $19,301/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P17" s="21" t="inlineStr">
@@ -24967,7 +24967,7 @@
           <t>Q | 435呎 (2房)
 $921万
 $21,166/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
           <t>A | 642呎 (3房)
 $1215万
 $18,927/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -24990,7 +24990,7 @@
           <t>B | 390呎 (2房)
 $824万
 $21,125/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -24998,7 +24998,7 @@
           <t>C | 388呎 (2房)
 $771万
 $19,877/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -25006,7 +25006,7 @@
           <t>D | 389呎 (2房)
 $808万
 $20,769/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -25014,7 +25014,7 @@
           <t>E | 393呎 (2房)
 $738万
 $18,788/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -25022,7 +25022,7 @@
           <t>F | 399呎 (2房)
 $745万
 $18,674/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -25030,7 +25030,7 @@
           <t>G | 398呎 (2房)
 $764万
 $19,200/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -25046,7 +25046,7 @@
           <t>J | 339呎 (2房)
 $669万
 $19,741/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -25054,7 +25054,7 @@
           <t>K | 339呎 (2房)
 $670万
 $19,765/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -25062,7 +25062,7 @@
           <t>L | 339呎 (2房)
 $689万
 $20,323/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
@@ -25070,7 +25070,7 @@
           <t>M | 339呎 (2房)
 $713万
 $21,038/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N18" s="21" t="inlineStr">
@@ -25078,7 +25078,7 @@
           <t>N | 339呎 (2房)
 $658万
 $19,416/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O18" s="21" t="inlineStr">
@@ -25086,7 +25086,7 @@
           <t>P | 343呎 (2房)
 $660万
 $19,237/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P18" s="21" t="inlineStr">
@@ -25094,7 +25094,7 @@
           <t>Q | 435呎 (2房)
 $870万
 $19,993/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -25109,7 +25109,7 @@
           <t>A | 642呎 (3房)
 $1211万
 $18,860/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -25117,7 +25117,7 @@
           <t>B | 390呎 (2房)
 $777万
 $19,917/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -25125,7 +25125,7 @@
           <t>C | 388呎 (2房)
 $768万
 $19,788/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -25133,7 +25133,7 @@
           <t>D | 389呎 (2房)
 $762万
 $19,580/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -25141,7 +25141,7 @@
           <t>E | 393呎 (2房)
 $761万
 $19,368/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -25149,7 +25149,7 @@
           <t>F | 399呎 (2房)
 $776万
 $19,443/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -25157,7 +25157,7 @@
           <t>G | 398呎 (2房)
 $722万
 $18,136/呎
-(26年-04月-24日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -25173,7 +25173,7 @@
           <t>J | 339呎 (2房)
 $667万
 $19,671/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -25181,7 +25181,7 @@
           <t>K | 339呎 (2房)
 $704万
 $20,777/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -25189,7 +25189,7 @@
           <t>L | 339呎 (2房)
 $722万
 $21,301/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M19" s="21" t="inlineStr">
@@ -25197,7 +25197,7 @@
           <t>M | 339呎 (2房)
 $709万
 $20,905/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N19" s="21" t="inlineStr">
@@ -25205,7 +25205,7 @@
           <t>N | 339呎 (2房)
 $656万
 $19,349/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O19" s="21" t="inlineStr">
@@ -25213,7 +25213,7 @@
           <t>P | 343呎 (2房)
 $658万
 $19,171/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P19" s="21" t="inlineStr">
@@ -25221,7 +25221,7 @@
           <t>Q | 435呎 (2房)
 $867万
 $19,924/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -25236,7 +25236,7 @@
           <t>A | 642呎 (3房)
 $1207万
 $18,794/呎
-(26年-04月-24日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -25244,7 +25244,7 @@
           <t>B | 390呎 (2房)
 $790万
 $20,245/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -25252,7 +25252,7 @@
           <t>C | 388呎 (2房)
 $761万
 $19,621/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -25260,7 +25260,7 @@
           <t>D | 389呎 (2房)
 $799万
 $20,545/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -25268,7 +25268,7 @@
           <t>E | 393呎 (2房)
 $708万
 $18,024/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -25276,7 +25276,7 @@
           <t>F | 399呎 (2房)
 $718万
 $18,004/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -25284,7 +25284,7 @@
           <t>G | 398呎 (2房)
 $759万
 $19,062/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -25300,7 +25300,7 @@
           <t>J | 339呎 (2房)
 $664万
 $19,596/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -25308,7 +25308,7 @@
           <t>K | 339呎 (2房)
 $665万
 $19,623/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -25316,7 +25316,7 @@
           <t>L | 339呎 (2房)
 $680万
 $20,063/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -25324,7 +25324,7 @@
           <t>M | 339呎 (2房)
 $668万
 $19,706/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N20" s="21" t="inlineStr">
@@ -25332,7 +25332,7 @@
           <t>N | 339呎 (2房)
 $654万
 $19,282/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O20" s="21" t="inlineStr">
@@ -25340,7 +25340,7 @@
           <t>P | 343呎 (2房)
 $655万
 $19,102/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P20" s="21" t="inlineStr">
@@ -25348,7 +25348,7 @@
           <t>Q | 435呎 (2房)
 $864万
 $19,853/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -25363,7 +25363,7 @@
           <t>A | 642呎 (3房)
 $1229万
 $19,137/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -25371,7 +25371,7 @@
           <t>B | 390呎 (2房)
 $786万
 $20,155/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -25379,7 +25379,7 @@
           <t>C | 388呎 (2房)
 $757万
 $19,516/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -25387,7 +25387,7 @@
           <t>D | 389呎 (2房)
 $752万
 $19,330/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -25395,7 +25395,7 @@
           <t>E | 393呎 (2房)
 $706万
 $17,961/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -25403,7 +25403,7 @@
           <t>F | 399呎 (2房)
 $716万
 $17,940/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -25411,7 +25411,7 @@
           <t>G | 398呎 (2房)
 $717万
 $18,006/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -25427,7 +25427,7 @@
           <t>J | 339呎 (2房)
 $662万
 $19,526/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -25435,7 +25435,7 @@
           <t>K | 339呎 (2房)
 $676万
 $19,944/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -25443,7 +25443,7 @@
           <t>L | 339呎 (2房)
 $676万
 $19,953/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -25451,7 +25451,7 @@
           <t>M | 339呎 (2房)
 $666万
 $19,636/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N21" s="21" t="inlineStr">
@@ -25459,7 +25459,7 @@
           <t>N | 339呎 (2房)
 $653万
 $19,250/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O21" s="21" t="inlineStr">
@@ -25467,7 +25467,7 @@
           <t>P | 343呎 (2房)
 $654万
 $19,078/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P21" s="21" t="inlineStr">
@@ -25475,7 +25475,7 @@
           <t>Q | 435呎 (2房)
 $861万
 $19,783/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -25490,7 +25490,7 @@
           <t>A | 642呎 (3房)
 $1198万
 $18,661/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -25498,7 +25498,7 @@
           <t>B | 390呎 (2房)
 $765万
 $19,612/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -25506,7 +25506,7 @@
           <t>C | 388呎 (2房)
 $796万
 $20,514/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -25514,7 +25514,7 @@
           <t>D | 389呎 (2房)
 $749万
 $19,243/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -25522,7 +25522,7 @@
           <t>E | 393呎 (2房)
 $703万
 $17,894/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -25530,7 +25530,7 @@
           <t>F | 399呎 (2房)
 $713万
 $17,876/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -25538,7 +25538,7 @@
           <t>G | 398呎 (2房)
 $730万
 $18,336/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -25554,7 +25554,7 @@
           <t>J | 339呎 (2房)
 $660万
 $19,456/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -25562,7 +25562,7 @@
           <t>K | 339呎 (2房)
 $656万
 $19,365/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -25570,7 +25570,7 @@
           <t>L | 339呎 (2房)
 $685万
 $20,196/呎
-(26年-04月-24日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -25578,7 +25578,7 @@
           <t>M | 339呎 (2房)
 $663万
 $19,563/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
@@ -25586,7 +25586,7 @@
           <t>N | 339呎 (2房)
 $651万
 $19,201/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O22" s="21" t="inlineStr">
@@ -25594,7 +25594,7 @@
           <t>P | 343呎 (2房)
 $653万
 $19,028/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P22" s="21" t="inlineStr">
@@ -25602,7 +25602,7 @@
           <t>Q | 435呎 (2房)
 $905万
 $20,793/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -25617,7 +25617,7 @@
           <t>A | 642呎 (3房)
 $1194万
 $18,594/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -25625,7 +25625,7 @@
           <t>B | 390呎 (2房)
 $802万
 $20,576/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -25633,7 +25633,7 @@
           <t>C | 388呎 (2房)
 $793万
 $20,439/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -25641,7 +25641,7 @@
           <t>D | 389呎 (2房)
 $746万
 $19,171/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -25649,7 +25649,7 @@
           <t>E | 393呎 (2房)
 $701万
 $17,830/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -25657,7 +25657,7 @@
           <t>F | 399呎 (2房)
 $750万
 $18,791/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -25665,7 +25665,7 @@
           <t>G | 398呎 (2房)
 $711万
 $17,875/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -25681,7 +25681,7 @@
           <t>J | 339呎 (2房)
 $693万
 $20,449/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -25689,7 +25689,7 @@
           <t>K | 339呎 (2房)
 $690万
 $20,353/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -25697,7 +25697,7 @@
           <t>L | 339呎 (2房)
 $664万
 $19,596/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -25705,7 +25705,7 @@
           <t>M | 339呎 (2房)
 $661万
 $19,494/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N23" s="21" t="inlineStr">
@@ -25713,7 +25713,7 @@
           <t>N | 339呎 (2房)
 $650万
 $19,172/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O23" s="21" t="inlineStr">
@@ -25721,7 +25721,7 @@
           <t>P | 343呎 (2房)
 $652万
 $18,999/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P23" s="21" t="inlineStr">
@@ -25729,7 +25729,7 @@
           <t>Q | 435呎 (2房)
 $854万
 $19,639/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -25744,7 +25744,7 @@
           <t>A | 642呎 (3房)
 $1218万
 $18,965/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -25752,7 +25752,7 @@
           <t>B | 390呎 (2房)
 $758万
 $19,429/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -25760,7 +25760,7 @@
           <t>C | 388呎 (2房)
 $789万
 $20,338/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -25768,7 +25768,7 @@
           <t>D | 389呎 (2房)
 $758万
 $19,496/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -25776,7 +25776,7 @@
           <t>E | 393呎 (2房)
 $699万
 $17,792/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -25784,7 +25784,7 @@
           <t>F | 399呎 (2房)
 $709万
 $17,776/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -25792,7 +25792,7 @@
           <t>G | 398呎 (2房)
 $710万
 $17,841/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -25808,7 +25808,7 @@
           <t>J | 339呎 (2房)
 $670万
 $19,768/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -25816,7 +25816,7 @@
           <t>K | 339呎 (2房)
 $667万
 $19,675/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -25824,7 +25824,7 @@
           <t>L | 339呎 (2房)
 $660万
 $19,464/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -25832,7 +25832,7 @@
           <t>M | 339呎 (2房)
 $659万
 $19,453/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N24" s="21" t="inlineStr">
@@ -25840,7 +25840,7 @@
           <t>N | 339呎 (2房)
 $646万
 $19,064/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O24" s="21" t="inlineStr">
@@ -25848,7 +25848,7 @@
           <t>P | 343呎 (2房)
 $651万
 $18,969/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P24" s="21" t="inlineStr">
@@ -25856,7 +25856,7 @@
           <t>Q | 435呎 (2房)
 $899万
 $20,668/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -25871,7 +25871,7 @@
           <t>A | 642呎 (3房)
 $1187万
 $18,495/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -25879,7 +25879,7 @@
           <t>B | 390呎 (2房)
 $755万
 $19,362/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -25887,7 +25887,7 @@
           <t>C | 388呎 (2房)
 $746万
 $19,215/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -25895,7 +25895,7 @@
           <t>D | 389呎 (2房)
 $756万
 $19,432/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -25903,7 +25903,7 @@
           <t>E | 393呎 (2房)
 $698万
 $17,765/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -25911,7 +25911,7 @@
           <t>F | 399呎 (2房)
 $708万
 $17,748/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -25919,7 +25919,7 @@
           <t>G | 398呎 (2房)
 $709万
 $17,811/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -25935,7 +25935,7 @@
           <t>J | 339呎 (2房)
 $688万
 $20,301/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -25943,7 +25943,7 @@
           <t>K | 339呎 (2房)
 $649万
 $19,153/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -25951,7 +25951,7 @@
           <t>L | 339呎 (2房)
 $656万
 $19,365/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -25959,7 +25959,7 @@
           <t>M | 339呎 (2房)
 $656万
 $19,349/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
@@ -25967,7 +25967,7 @@
           <t>N | 339呎 (2房)
 $645万
 $19,035/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O25" s="21" t="inlineStr">
@@ -25975,7 +25975,7 @@
           <t>P | 343呎 (2房)
 $647万
 $18,863/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P25" s="21" t="inlineStr">
@@ -25983,7 +25983,7 @@
           <t>Q | 435呎 (2房)
 $848万
 $19,497/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -25998,7 +25998,7 @@
           <t>A | 642呎 (3房)
 $1185万
 $18,461/呎
-(26年-04月-24日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -26006,7 +26006,7 @@
           <t>B | 390呎 (2房)
 $752万
 $19,292/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -26014,7 +26014,7 @@
           <t>C | 388呎 (2房)
 $741万
 $19,089/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -26022,7 +26022,7 @@
           <t>D | 389呎 (2房)
 $735万
 $18,888/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -26030,7 +26030,7 @@
           <t>E | 393呎 (2房)
 $697万
 $17,734/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -26038,7 +26038,7 @@
           <t>F | 399呎 (2房)
 $707万
 $17,719/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -26046,7 +26046,7 @@
           <t>G | 398呎 (2房)
 $746万
 $18,756/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -26054,7 +26054,7 @@
           <t>H | 399呎 (2房)
 $698万
 $17,481/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -26062,7 +26062,7 @@
           <t>J | 339呎 (2房)
 $650万
 $19,169/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -26070,7 +26070,7 @@
           <t>K | 339呎 (2房)
 $661万
 $19,500/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -26078,7 +26078,7 @@
           <t>L | 339呎 (2房)
 $654万
 $19,292/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -26086,7 +26086,7 @@
           <t>M | 339呎 (2房)
 $654万
 $19,279/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N26" s="21" t="inlineStr">
@@ -26094,7 +26094,7 @@
           <t>N | 339呎 (2房)
 $643万
 $18,968/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O26" s="21" t="inlineStr">
@@ -26102,7 +26102,7 @@
           <t>P | 343呎 (2房)
 $645万
 $18,797/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P26" s="21" t="inlineStr">
@@ -26110,7 +26110,7 @@
           <t>Q | 435呎 (2房)
 $864万
 $19,853/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -26125,7 +26125,7 @@
           <t>A | 642呎 (3房)
 $1183万
 $18,427/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -26133,7 +26133,7 @@
           <t>B | 390呎 (2房)
 $751万
 $19,255/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -26141,7 +26141,7 @@
           <t>C | 388呎 (2房)
 $753万
 $19,415/呎
-(26年-04月-24日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -26149,7 +26149,7 @@
           <t>D | 389呎 (2房)
 $730万
 $18,764/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -26157,7 +26157,7 @@
           <t>E | 393呎 (2房)
 $696万
 $17,700/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -26165,7 +26165,7 @@
           <t>F | 399呎 (2房)
 $706万
 $17,684/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -26173,7 +26173,7 @@
           <t>G | 398呎 (2房)
 $703万
 $17,660/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -26181,7 +26181,7 @@
           <t>H | 399呎 (2房)
 $693万
 $17,365/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -26189,7 +26189,7 @@
           <t>J | 339呎 (2房)
 $678万
 $19,996/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -26197,7 +26197,7 @@
           <t>K | 339呎 (2房)
 $641万
 $18,919/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -26205,7 +26205,7 @@
           <t>L | 339呎 (2房)
 $648万
 $19,129/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -26213,7 +26213,7 @@
           <t>M | 339呎 (2房)
 $648万
 $19,115/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N27" s="21" t="inlineStr">
@@ -26221,7 +26221,7 @@
           <t>N | 339呎 (2房)
 $673万
 $19,854/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O27" s="21" t="inlineStr">
@@ -26229,7 +26229,7 @@
           <t>P | 343呎 (2房)
 $657万
 $19,142/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P27" s="21" t="inlineStr">
@@ -26237,7 +26237,7 @@
           <t>Q | 435呎 (2房)
 $842万
 $19,355/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -26316,7 +26316,7 @@
           <t>J | 301呎 (2房)
 $714万
 $23,708/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -26324,7 +26324,7 @@
           <t>K | 301呎 (2房)
 $715万
 $23,742/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -26332,7 +26332,7 @@
           <t>L | 301呎 (2房)
 $705万
 $23,424/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -26340,7 +26340,7 @@
           <t>M | 301呎 (2房)
 $690万
 $22,907/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N28" s="21" t="inlineStr">
@@ -26348,7 +26348,7 @@
           <t>N | 301呎 (2房)
 $687万
 $22,822/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O28" s="21" t="inlineStr">
@@ -26356,7 +26356,7 @@
           <t>P | 306呎 (2房)
 $701万
 $22,922/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P28" s="21" t="inlineStr">
@@ -26364,7 +26364,7 @@
           <t>Q | 435呎 (2房)
 $912万
 $20,956/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-红磡-首岸第1期.xlsx
+++ b/files/九龙-红磡-首岸第1期.xlsx
@@ -23339,7 +23339,7 @@
           <t>B | 390呎 (2房)
 $861万
 $22,085/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -23347,7 +23347,7 @@
           <t>C | 388呎 (2房)
 $847万
 $21,830/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -23355,7 +23355,7 @@
           <t>D | 389呎 (2房)
 $841万
 $21,620/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -23363,7 +23363,7 @@
           <t>E | 393呎 (2房)
 $841万
 $21,400/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -23371,7 +23371,7 @@
           <t>F | 399呎 (2房)
 $860万
 $21,541/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -23379,7 +23379,7 @@
           <t>G | 398呎 (2房)
 $830万
 $20,857/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="I5" s="21" t="inlineStr">
@@ -23387,7 +23387,7 @@
           <t>H | 399呎 (2房)
 $824万
 $20,652/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -23395,7 +23395,7 @@
           <t>J | 339呎 (2房)
 $756万
 $22,315/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="K5" s="21" t="inlineStr">
@@ -23403,7 +23403,7 @@
           <t>K | 339呎 (2房)
 $764万
 $22,540/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
@@ -23411,7 +23411,7 @@
           <t>L | 339呎 (2房)
 $780万
 $23,017/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="M5" s="21" t="inlineStr">
@@ -23419,7 +23419,7 @@
           <t>M | 339呎 (2房)
 $740万
 $21,818/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="N5" s="21" t="inlineStr">
@@ -23427,7 +23427,7 @@
           <t>N | 339呎 (2房)
 $726万
 $21,427/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="O5" s="21" t="inlineStr">
@@ -23435,7 +23435,7 @@
           <t>P | 343呎 (2房)
 $721万
 $21,017/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="P5" s="20" t="inlineStr">
@@ -23458,7 +23458,7 @@
           <t>A | 642呎 (3房)
 $1400万
 $21,805/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -23466,7 +23466,7 @@
           <t>B | 390呎 (2房)
 $857万
 $21,968/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -23474,7 +23474,7 @@
           <t>C | 388呎 (2房)
 $841万
 $21,678/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -23482,7 +23482,7 @@
           <t>D | 389呎 (2房)
 $835万
 $21,463/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -23490,7 +23490,7 @@
           <t>E | 393呎 (2房)
 $853万
 $21,714/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -23498,7 +23498,7 @@
           <t>F | 399呎 (2房)
 $835万
 $20,930/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -23506,7 +23506,7 @@
           <t>G | 398呎 (2房)
 $820万
 $20,614/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -23514,7 +23514,7 @@
           <t>H | 399呎 (2房)
 $814万
 $20,410/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -23522,7 +23522,7 @@
           <t>J | 339呎 (2房)
 $745万
 $21,969/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -23530,7 +23530,7 @@
           <t>K | 339呎 (2房)
 $747万
 $22,033/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -23538,7 +23538,7 @@
           <t>L | 339呎 (2房)
 $770万
 $22,707/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -23546,7 +23546,7 @@
           <t>M | 339呎 (2房)
 $729万
 $21,510/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
@@ -23554,7 +23554,7 @@
           <t>N | 339呎 (2房)
 $720万
 $21,225/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="O6" s="21" t="inlineStr">
@@ -23562,7 +23562,7 @@
           <t>P | 343呎 (2房)
 $714万
 $20,829/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="P6" s="21" t="inlineStr">
@@ -23570,7 +23570,7 @@
           <t>Q | 435呎 (2房)
 $927万
 $21,321/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -23585,7 +23585,7 @@
           <t>A | 642呎 (3房)
 $1387万
 $21,600/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -23593,7 +23593,7 @@
           <t>B | 390呎 (2房)
 $852万
 $21,858/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -23601,7 +23601,7 @@
           <t>C | 388呎 (2房)
 $853万
 $21,984/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -23609,7 +23609,7 @@
           <t>D | 389呎 (2房)
 $849万
 $21,828/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -23617,7 +23617,7 @@
           <t>E | 393呎 (2房)
 $829万
 $21,085/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -23625,7 +23625,7 @@
           <t>F | 399呎 (2房)
 $827万
 $20,722/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -23633,7 +23633,7 @@
           <t>G | 398呎 (2房)
 $812万
 $20,411/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -23641,7 +23641,7 @@
           <t>H | 399呎 (2房)
 $803万
 $20,129/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -23649,7 +23649,7 @@
           <t>J | 339呎 (2房)
 $735万
 $21,681/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -23657,7 +23657,7 @@
           <t>K | 339呎 (2房)
 $776万
 $22,904/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -23665,7 +23665,7 @@
           <t>L | 339呎 (2房)
 $747万
 $22,033/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="M7" s="21" t="inlineStr">
@@ -23673,7 +23673,7 @@
           <t>M | 339呎 (2房)
 $722万
 $21,303/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
@@ -23681,7 +23681,7 @@
           <t>N | 339呎 (2房)
 $713万
 $21,024/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -23689,7 +23689,7 @@
           <t>P | 343呎 (2房)
 $709万
 $20,670/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="P7" s="21" t="inlineStr">
@@ -23697,7 +23697,7 @@
           <t>Q | 435呎 (2房)
 $919万
 $21,135/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -23712,7 +23712,7 @@
           <t>A | 642呎 (3房)
 $1377万
 $21,444/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -23720,7 +23720,7 @@
           <t>B | 390呎 (2房)
 $848万
 $21,749/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -23728,7 +23728,7 @@
           <t>C | 388呎 (2房)
 $827万
 $21,324/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -23736,7 +23736,7 @@
           <t>D | 389呎 (2房)
 $827万
 $21,271/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -23744,7 +23744,7 @@
           <t>E | 393呎 (2房)
 $825万
 $20,997/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -23752,7 +23752,7 @@
           <t>F | 399呎 (2房)
 $818万
 $20,508/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -23760,7 +23760,7 @@
           <t>G | 398呎 (2房)
 $802万
 $20,159/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -23768,7 +23768,7 @@
           <t>H | 399呎 (2房)
 $795万
 $19,922/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -23776,7 +23776,7 @@
           <t>J | 339呎 (2房)
 $725万
 $21,378/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -23784,7 +23784,7 @@
           <t>K | 339呎 (2房)
 $726万
 $21,408/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -23792,7 +23792,7 @@
           <t>L | 339呎 (2房)
 $740万
 $21,827/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -23800,7 +23800,7 @@
           <t>M | 339呎 (2房)
 $731万
 $21,563/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
@@ -23808,7 +23808,7 @@
           <t>N | 339呎 (2房)
 $722万
 $21,286/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="O8" s="21" t="inlineStr">
@@ -23816,7 +23816,7 @@
           <t>P | 343呎 (2房)
 $720万
 $20,986/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="P8" s="21" t="inlineStr">
@@ -23824,7 +23824,7 @@
           <t>Q | 435呎 (2房)
 $912万
 $20,955/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -23839,7 +23839,7 @@
           <t>A | 642呎 (3房)
 $1367万
 $21,296/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -23847,7 +23847,7 @@
           <t>B | 390呎 (2房)
 $844万
 $21,637/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -23855,7 +23855,7 @@
           <t>C | 388呎 (2房)
 $821万
 $21,153/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -23863,7 +23863,7 @@
           <t>D | 389呎 (2房)
 $823万
 $21,161/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -23871,7 +23871,7 @@
           <t>E | 393呎 (2房)
 $819万
 $20,828/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -23879,7 +23879,7 @@
           <t>F | 399呎 (2房)
 $856万
 $21,462/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -23887,7 +23887,7 @@
           <t>G | 398呎 (2房)
 $796万
 $19,997/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -23895,7 +23895,7 @@
           <t>H | 399呎 (2房)
 $788万
 $19,758/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -23903,7 +23903,7 @@
           <t>J | 339呎 (2房)
 $733万
 $21,623/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -23911,7 +23911,7 @@
           <t>K | 339呎 (2房)
 $715万
 $21,086/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -23919,7 +23919,7 @@
           <t>L | 339呎 (2房)
 $732万
 $21,582/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
@@ -23927,7 +23927,7 @@
           <t>M | 339呎 (2房)
 $725万
 $21,398/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -23935,7 +23935,7 @@
           <t>N | 339呎 (2房)
 $698万
 $20,594/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="O9" s="21" t="inlineStr">
@@ -23943,7 +23943,7 @@
           <t>P | 343呎 (2房)
 $735万
 $21,439/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="P9" s="21" t="inlineStr">
@@ -23951,7 +23951,7 @@
           <t>Q | 435呎 (2房)
 $905万
 $20,809/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -23966,7 +23966,7 @@
           <t>A | 642呎 (3房)
 $1359万
 $21,165/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -23974,7 +23974,7 @@
           <t>B | 390呎 (2房)
 $838万
 $21,483/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -23982,7 +23982,7 @@
           <t>C | 388呎 (2房)
 $860万
 $22,176/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -23990,7 +23990,7 @@
           <t>D | 389呎 (2房)
 $864万
 $22,223/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -23998,7 +23998,7 @@
           <t>E | 393呎 (2房)
 $857万
 $21,794/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -24006,7 +24006,7 @@
           <t>F | 399呎 (2房)
 $852万
 $21,348/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -24014,7 +24014,7 @@
           <t>G | 398呎 (2房)
 $789万
 $19,835/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -24022,7 +24022,7 @@
           <t>H | 399呎 (2房)
 $799万
 $20,031/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -24030,7 +24030,7 @@
           <t>J | 339呎 (2房)
 $713万
 $21,024/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -24038,7 +24038,7 @@
           <t>K | 339呎 (2房)
 $709万
 $20,917/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -24046,7 +24046,7 @@
           <t>L | 339呎 (2房)
 $766万
 $22,606/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -24054,7 +24054,7 @@
           <t>M | 339呎 (2房)
 $722万
 $21,286/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -24062,7 +24062,7 @@
           <t>N | 339呎 (2房)
 $694万
 $20,468/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="O10" s="21" t="inlineStr">
@@ -24070,7 +24070,7 @@
           <t>P | 343呎 (2房)
 $688万
 $20,065/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="P10" s="21" t="inlineStr">
@@ -24078,7 +24078,7 @@
           <t>Q | 435呎 (2房)
 $898万
 $20,639/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -24093,7 +24093,7 @@
           <t>A | 642呎 (3房)
 $1350万
 $21,035/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -24101,7 +24101,7 @@
           <t>B | 390呎 (2房)
 $849万
 $21,778/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -24109,7 +24109,7 @@
           <t>C | 388呎 (2房)
 $811万
 $20,909/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -24117,7 +24117,7 @@
           <t>D | 389呎 (2房)
 $814万
 $20,914/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -24125,7 +24125,7 @@
           <t>E | 393呎 (2房)
 $809万
 $20,592/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -24133,7 +24133,7 @@
           <t>F | 399呎 (2房)
 $845万
 $21,180/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -24141,7 +24141,7 @@
           <t>G | 398呎 (2房)
 $779万
 $19,581/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -24149,7 +24149,7 @@
           <t>H | 399呎 (2房)
 $775万
 $19,420/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -24157,7 +24157,7 @@
           <t>J | 339呎 (2房)
 $709万
 $20,914/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -24165,7 +24165,7 @@
           <t>K | 339呎 (2房)
 $747万
 $22,029/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -24173,7 +24173,7 @@
           <t>L | 339呎 (2房)
 $762万
 $22,488/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
@@ -24181,7 +24181,7 @@
           <t>M | 339呎 (2房)
 $742万
 $21,876/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -24189,7 +24189,7 @@
           <t>N | 339呎 (2房)
 $705万
 $20,808/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="O11" s="21" t="inlineStr">
@@ -24197,7 +24197,7 @@
           <t>P | 343呎 (2房)
 $686万
 $19,999/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="P11" s="21" t="inlineStr">
@@ -24205,7 +24205,7 @@
           <t>Q | 435呎 (2房)
 $891万
 $20,489/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
           <t>A | 642呎 (3房)
 $1340万
 $20,866/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -24228,7 +24228,7 @@
           <t>B | 390呎 (2房)
 $825万
 $21,142/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -24236,7 +24236,7 @@
           <t>C | 388呎 (2房)
 $806万
 $20,777/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -24244,7 +24244,7 @@
           <t>D | 389呎 (2房)
 $852万
 $21,905/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -24252,7 +24252,7 @@
           <t>E | 393呎 (2房)
 $802万
 $20,416/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -24260,7 +24260,7 @@
           <t>F | 399呎 (2房)
 $795万
 $19,931/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -24268,7 +24268,7 @@
           <t>G | 398呎 (2房)
 $769万
 $19,327/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -24276,7 +24276,7 @@
           <t>H | 399呎 (2房)
 $811万
 $20,336/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -24284,7 +24284,7 @@
           <t>J | 339呎 (2房)
 $703万
 $20,745/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -24292,7 +24292,7 @@
           <t>K | 339呎 (2房)
 $704万
 $20,771/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -24300,7 +24300,7 @@
           <t>L | 339呎 (2房)
 $718万
 $21,185/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
@@ -24308,7 +24308,7 @@
           <t>M | 339呎 (2房)
 $738万
 $21,757/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -24316,7 +24316,7 @@
           <t>N | 339呎 (2房)
 $686万
 $20,251/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="O12" s="21" t="inlineStr">
@@ -24324,7 +24324,7 @@
           <t>P | 343呎 (2房)
 $684万
 $19,927/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="P12" s="21" t="inlineStr">
@@ -24332,7 +24332,7 @@
           <t>Q | 435呎 (2房)
 $888万
 $20,420/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -24347,7 +24347,7 @@
           <t>A | 642呎 (3房)
 $1345万
 $20,945/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -24355,7 +24355,7 @@
           <t>B | 390呎 (2房)
 $818万
 $20,972/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -24363,7 +24363,7 @@
           <t>C | 388呎 (2房)
 $799万
 $20,597/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -24371,7 +24371,7 @@
           <t>D | 389呎 (2房)
 $845万
 $21,712/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -24379,7 +24379,7 @@
           <t>E | 393呎 (2房)
 $796万
 $20,242/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -24387,7 +24387,7 @@
           <t>F | 399呎 (2房)
 $786万
 $19,696/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -24395,7 +24395,7 @@
           <t>G | 398呎 (2房)
 $741万
 $18,621/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -24403,7 +24403,7 @@
           <t>H | 399呎 (2房)
 $805万
 $20,172/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -24411,7 +24411,7 @@
           <t>J | 339呎 (2房)
 $735万
 $21,686/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -24419,7 +24419,7 @@
           <t>K | 339呎 (2房)
 $695万
 $20,503/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -24427,7 +24427,7 @@
           <t>L | 339呎 (2房)
 $715万
 $21,091/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
@@ -24435,7 +24435,7 @@
           <t>M | 339呎 (2房)
 $734万
 $21,641/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -24443,7 +24443,7 @@
           <t>N | 339呎 (2房)
 $699万
 $20,605/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="O13" s="21" t="inlineStr">
@@ -24451,7 +24451,7 @@
           <t>P | 343呎 (2房)
 $719万
 $20,952/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="P13" s="21" t="inlineStr">
@@ -24459,7 +24459,7 @@
           <t>Q | 435呎 (2房)
 $885万
 $20,348/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -24474,7 +24474,7 @@
           <t>A | 642呎 (3房)
 $1320万
 $20,567/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -24482,7 +24482,7 @@
           <t>B | 390呎 (2房)
 $810万
 $20,778/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -24490,7 +24490,7 @@
           <t>C | 388呎 (2房)
 $792万
 $20,419/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -24498,7 +24498,7 @@
           <t>D | 389呎 (2房)
 $810万
 $20,835/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -24506,7 +24506,7 @@
           <t>E | 393呎 (2房)
 $798万
 $20,306/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -24514,7 +24514,7 @@
           <t>F | 399呎 (2房)
 $779万
 $19,518/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -24522,7 +24522,7 @@
           <t>G | 398呎 (2房)
 $738万
 $18,554/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -24538,7 +24538,7 @@
           <t>J | 339呎 (2房)
 $690万
 $20,369/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -24546,7 +24546,7 @@
           <t>K | 339呎 (2房)
 $686万
 $20,240/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -24554,7 +24554,7 @@
           <t>L | 339呎 (2房)
 $712万
 $20,997/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -24562,7 +24562,7 @@
           <t>M | 339呎 (2房)
 $729万
 $21,505/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -24570,7 +24570,7 @@
           <t>N | 339呎 (2房)
 $681万
 $20,076/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="O14" s="21" t="inlineStr">
@@ -24578,7 +24578,7 @@
           <t>P | 343呎 (2房)
 $676万
 $19,701/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="P14" s="21" t="inlineStr">
@@ -24586,7 +24586,7 @@
           <t>Q | 435呎 (2房)
 $882万
 $20,277/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -24601,7 +24601,7 @@
           <t>A | 642呎 (3房)
 $1301万
 $20,270/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -24609,7 +24609,7 @@
           <t>B | 390呎 (2房)
 $802万
 $20,564/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -24617,7 +24617,7 @@
           <t>C | 388呎 (2房)
 $786万
 $20,245/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -24625,7 +24625,7 @@
           <t>D | 389呎 (2房)
 $803万
 $20,637/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -24633,7 +24633,7 @@
           <t>E | 393呎 (2房)
 $774万
 $19,707/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -24641,7 +24641,7 @@
           <t>F | 399呎 (2房)
 $772万
 $19,338/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -24649,7 +24649,7 @@
           <t>G | 398呎 (2房)
 $736万
 $18,490/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -24665,7 +24665,7 @@
           <t>J | 339呎 (2房)
 $683万
 $20,146/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -24673,7 +24673,7 @@
           <t>K | 339呎 (2房)
 $677万
 $19,974/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -24681,7 +24681,7 @@
           <t>L | 339呎 (2房)
 $704万
 $20,771/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr">
@@ -24689,7 +24689,7 @@
           <t>M | 339呎 (2房)
 $726万
 $21,409/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -24697,7 +24697,7 @@
           <t>N | 339呎 (2房)
 $675万
 $19,912/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="O15" s="21" t="inlineStr">
@@ -24705,7 +24705,7 @@
           <t>P | 343呎 (2房)
 $673万
 $19,633/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="P15" s="21" t="inlineStr">
@@ -24713,7 +24713,7 @@
           <t>Q | 435呎 (2房)
 $879万
 $20,208/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -24728,7 +24728,7 @@
           <t>A | 642呎 (3房)
 $1251万
 $19,491/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -24736,7 +24736,7 @@
           <t>B | 390呎 (2房)
 $796万
 $20,403/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -24744,7 +24744,7 @@
           <t>C | 388呎 (2房)
 $799万
 $20,585/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -24752,7 +24752,7 @@
           <t>D | 389呎 (2房)
 $778万
 $19,999/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -24760,7 +24760,7 @@
           <t>E | 393呎 (2房)
 $763万
 $19,422/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -24768,7 +24768,7 @@
           <t>F | 399呎 (2房)
 $766万
 $19,187/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -24776,7 +24776,7 @@
           <t>G | 398呎 (2房)
 $732万
 $18,396/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -24792,7 +24792,7 @@
           <t>J | 339呎 (2房)
 $689万
 $20,331/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -24800,7 +24800,7 @@
           <t>K | 339呎 (2房)
 $712万
 $21,009/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -24808,7 +24808,7 @@
           <t>L | 339呎 (2房)
 $699万
 $20,608/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -24816,7 +24816,7 @@
           <t>M | 339呎 (2房)
 $700万
 $20,635/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="N16" s="21" t="inlineStr">
@@ -24824,7 +24824,7 @@
           <t>N | 339呎 (2房)
 $666万
 $19,660/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="O16" s="21" t="inlineStr">
@@ -24832,7 +24832,7 @@
           <t>P | 343呎 (2房)
 $668万
 $19,476/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="P16" s="21" t="inlineStr">
@@ -24840,7 +24840,7 @@
           <t>Q | 435呎 (2房)
 $876万
 $20,143/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -24855,7 +24855,7 @@
           <t>A | 642呎 (3房)
 $1231万
 $19,178/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -24863,7 +24863,7 @@
           <t>B | 390呎 (2房)
 $832万
 $21,336/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -24871,7 +24871,7 @@
           <t>C | 388呎 (2房)
 $776万
 $20,001/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -24879,7 +24879,7 @@
           <t>D | 389呎 (2房)
 $788万
 $20,250/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -24887,7 +24887,7 @@
           <t>E | 393呎 (2房)
 $751万
 $19,105/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -24895,7 +24895,7 @@
           <t>F | 399呎 (2房)
 $797万
 $19,963/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -24903,7 +24903,7 @@
           <t>G | 398呎 (2房)
 $727万
 $18,264/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -24919,7 +24919,7 @@
           <t>J | 339呎 (2房)
 $686万
 $20,249/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -24927,7 +24927,7 @@
           <t>K | 339呎 (2房)
 $687万
 $20,273/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -24935,7 +24935,7 @@
           <t>L | 339呎 (2房)
 $693万
 $20,452/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
@@ -24943,7 +24943,7 @@
           <t>M | 339呎 (2房)
 $719万
 $21,216/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
@@ -24951,7 +24951,7 @@
           <t>N | 339呎 (2房)
 $661万
 $19,486/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="O17" s="21" t="inlineStr">
@@ -24959,7 +24959,7 @@
           <t>P | 343呎 (2房)
 $662万
 $19,301/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="P17" s="21" t="inlineStr">
@@ -24967,7 +24967,7 @@
           <t>Q | 435呎 (2房)
 $921万
 $21,166/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
           <t>A | 642呎 (3房)
 $1215万
 $18,927/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -24990,7 +24990,7 @@
           <t>B | 390呎 (2房)
 $824万
 $21,125/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -24998,7 +24998,7 @@
           <t>C | 388呎 (2房)
 $771万
 $19,877/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -25006,7 +25006,7 @@
           <t>D | 389呎 (2房)
 $808万
 $20,769/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -25014,7 +25014,7 @@
           <t>E | 393呎 (2房)
 $738万
 $18,788/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -25022,7 +25022,7 @@
           <t>F | 399呎 (2房)
 $745万
 $18,674/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -25030,7 +25030,7 @@
           <t>G | 398呎 (2房)
 $764万
 $19,200/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -25046,7 +25046,7 @@
           <t>J | 339呎 (2房)
 $669万
 $19,741/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -25054,7 +25054,7 @@
           <t>K | 339呎 (2房)
 $670万
 $19,765/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -25062,7 +25062,7 @@
           <t>L | 339呎 (2房)
 $689万
 $20,323/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
@@ -25070,7 +25070,7 @@
           <t>M | 339呎 (2房)
 $713万
 $21,038/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="N18" s="21" t="inlineStr">
@@ -25078,7 +25078,7 @@
           <t>N | 339呎 (2房)
 $658万
 $19,416/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="O18" s="21" t="inlineStr">
@@ -25086,7 +25086,7 @@
           <t>P | 343呎 (2房)
 $660万
 $19,237/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="P18" s="21" t="inlineStr">
@@ -25094,7 +25094,7 @@
           <t>Q | 435呎 (2房)
 $870万
 $19,993/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -25109,7 +25109,7 @@
           <t>A | 642呎 (3房)
 $1211万
 $18,860/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -25117,7 +25117,7 @@
           <t>B | 390呎 (2房)
 $777万
 $19,917/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -25125,7 +25125,7 @@
           <t>C | 388呎 (2房)
 $768万
 $19,788/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -25133,7 +25133,7 @@
           <t>D | 389呎 (2房)
 $762万
 $19,580/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -25141,7 +25141,7 @@
           <t>E | 393呎 (2房)
 $761万
 $19,368/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -25149,7 +25149,7 @@
           <t>F | 399呎 (2房)
 $776万
 $19,443/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -25157,7 +25157,7 @@
           <t>G | 398呎 (2房)
 $722万
 $18,136/呎
-(26年-04月)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -25173,7 +25173,7 @@
           <t>J | 339呎 (2房)
 $667万
 $19,671/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -25181,7 +25181,7 @@
           <t>K | 339呎 (2房)
 $704万
 $20,777/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -25189,7 +25189,7 @@
           <t>L | 339呎 (2房)
 $722万
 $21,301/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="M19" s="21" t="inlineStr">
@@ -25197,7 +25197,7 @@
           <t>M | 339呎 (2房)
 $709万
 $20,905/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="N19" s="21" t="inlineStr">
@@ -25205,7 +25205,7 @@
           <t>N | 339呎 (2房)
 $656万
 $19,349/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="O19" s="21" t="inlineStr">
@@ -25213,7 +25213,7 @@
           <t>P | 343呎 (2房)
 $658万
 $19,171/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="P19" s="21" t="inlineStr">
@@ -25221,7 +25221,7 @@
           <t>Q | 435呎 (2房)
 $867万
 $19,924/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -25236,7 +25236,7 @@
           <t>A | 642呎 (3房)
 $1207万
 $18,794/呎
-(26年-04月)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -25244,7 +25244,7 @@
           <t>B | 390呎 (2房)
 $790万
 $20,245/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -25252,7 +25252,7 @@
           <t>C | 388呎 (2房)
 $761万
 $19,621/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -25260,7 +25260,7 @@
           <t>D | 389呎 (2房)
 $799万
 $20,545/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -25268,7 +25268,7 @@
           <t>E | 393呎 (2房)
 $708万
 $18,024/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -25276,7 +25276,7 @@
           <t>F | 399呎 (2房)
 $718万
 $18,004/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -25284,7 +25284,7 @@
           <t>G | 398呎 (2房)
 $759万
 $19,062/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -25300,7 +25300,7 @@
           <t>J | 339呎 (2房)
 $664万
 $19,596/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -25308,7 +25308,7 @@
           <t>K | 339呎 (2房)
 $665万
 $19,623/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -25316,7 +25316,7 @@
           <t>L | 339呎 (2房)
 $680万
 $20,063/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -25324,7 +25324,7 @@
           <t>M | 339呎 (2房)
 $668万
 $19,706/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N20" s="21" t="inlineStr">
@@ -25332,7 +25332,7 @@
           <t>N | 339呎 (2房)
 $654万
 $19,282/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="O20" s="21" t="inlineStr">
@@ -25340,7 +25340,7 @@
           <t>P | 343呎 (2房)
 $655万
 $19,102/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="P20" s="21" t="inlineStr">
@@ -25348,7 +25348,7 @@
           <t>Q | 435呎 (2房)
 $864万
 $19,853/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -25363,7 +25363,7 @@
           <t>A | 642呎 (3房)
 $1229万
 $19,137/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -25371,7 +25371,7 @@
           <t>B | 390呎 (2房)
 $786万
 $20,155/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -25379,7 +25379,7 @@
           <t>C | 388呎 (2房)
 $757万
 $19,516/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -25387,7 +25387,7 @@
           <t>D | 389呎 (2房)
 $752万
 $19,330/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -25395,7 +25395,7 @@
           <t>E | 393呎 (2房)
 $706万
 $17,961/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -25403,7 +25403,7 @@
           <t>F | 399呎 (2房)
 $716万
 $17,940/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -25411,7 +25411,7 @@
           <t>G | 398呎 (2房)
 $717万
 $18,006/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -25427,7 +25427,7 @@
           <t>J | 339呎 (2房)
 $662万
 $19,526/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -25435,7 +25435,7 @@
           <t>K | 339呎 (2房)
 $676万
 $19,944/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -25443,7 +25443,7 @@
           <t>L | 339呎 (2房)
 $676万
 $19,953/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -25451,7 +25451,7 @@
           <t>M | 339呎 (2房)
 $666万
 $19,636/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N21" s="21" t="inlineStr">
@@ -25459,7 +25459,7 @@
           <t>N | 339呎 (2房)
 $653万
 $19,250/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="O21" s="21" t="inlineStr">
@@ -25467,7 +25467,7 @@
           <t>P | 343呎 (2房)
 $654万
 $19,078/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="P21" s="21" t="inlineStr">
@@ -25475,7 +25475,7 @@
           <t>Q | 435呎 (2房)
 $861万
 $19,783/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -25490,7 +25490,7 @@
           <t>A | 642呎 (3房)
 $1198万
 $18,661/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -25498,7 +25498,7 @@
           <t>B | 390呎 (2房)
 $765万
 $19,612/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -25506,7 +25506,7 @@
           <t>C | 388呎 (2房)
 $796万
 $20,514/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -25514,7 +25514,7 @@
           <t>D | 389呎 (2房)
 $749万
 $19,243/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -25522,7 +25522,7 @@
           <t>E | 393呎 (2房)
 $703万
 $17,894/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -25530,7 +25530,7 @@
           <t>F | 399呎 (2房)
 $713万
 $17,876/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -25538,7 +25538,7 @@
           <t>G | 398呎 (2房)
 $730万
 $18,336/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -25554,7 +25554,7 @@
           <t>J | 339呎 (2房)
 $660万
 $19,456/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -25562,7 +25562,7 @@
           <t>K | 339呎 (2房)
 $656万
 $19,365/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -25570,7 +25570,7 @@
           <t>L | 339呎 (2房)
 $685万
 $20,196/呎
-(26年-04月)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -25578,7 +25578,7 @@
           <t>M | 339呎 (2房)
 $663万
 $19,563/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
@@ -25586,7 +25586,7 @@
           <t>N | 339呎 (2房)
 $651万
 $19,201/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="O22" s="21" t="inlineStr">
@@ -25594,7 +25594,7 @@
           <t>P | 343呎 (2房)
 $653万
 $19,028/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="P22" s="21" t="inlineStr">
@@ -25602,7 +25602,7 @@
           <t>Q | 435呎 (2房)
 $905万
 $20,793/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -25617,7 +25617,7 @@
           <t>A | 642呎 (3房)
 $1194万
 $18,594/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -25625,7 +25625,7 @@
           <t>B | 390呎 (2房)
 $802万
 $20,576/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -25633,7 +25633,7 @@
           <t>C | 388呎 (2房)
 $793万
 $20,439/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -25641,7 +25641,7 @@
           <t>D | 389呎 (2房)
 $746万
 $19,171/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -25649,7 +25649,7 @@
           <t>E | 393呎 (2房)
 $701万
 $17,830/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -25657,7 +25657,7 @@
           <t>F | 399呎 (2房)
 $750万
 $18,791/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -25665,7 +25665,7 @@
           <t>G | 398呎 (2房)
 $711万
 $17,875/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -25681,7 +25681,7 @@
           <t>J | 339呎 (2房)
 $693万
 $20,449/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -25689,7 +25689,7 @@
           <t>K | 339呎 (2房)
 $690万
 $20,353/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -25697,7 +25697,7 @@
           <t>L | 339呎 (2房)
 $664万
 $19,596/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -25705,7 +25705,7 @@
           <t>M | 339呎 (2房)
 $661万
 $19,494/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N23" s="21" t="inlineStr">
@@ -25713,7 +25713,7 @@
           <t>N | 339呎 (2房)
 $650万
 $19,172/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="O23" s="21" t="inlineStr">
@@ -25721,7 +25721,7 @@
           <t>P | 343呎 (2房)
 $652万
 $18,999/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="P23" s="21" t="inlineStr">
@@ -25729,7 +25729,7 @@
           <t>Q | 435呎 (2房)
 $854万
 $19,639/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -25744,7 +25744,7 @@
           <t>A | 642呎 (3房)
 $1218万
 $18,965/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -25752,7 +25752,7 @@
           <t>B | 390呎 (2房)
 $758万
 $19,429/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -25760,7 +25760,7 @@
           <t>C | 388呎 (2房)
 $789万
 $20,338/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -25768,7 +25768,7 @@
           <t>D | 389呎 (2房)
 $758万
 $19,496/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -25776,7 +25776,7 @@
           <t>E | 393呎 (2房)
 $699万
 $17,792/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -25784,7 +25784,7 @@
           <t>F | 399呎 (2房)
 $709万
 $17,776/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -25792,7 +25792,7 @@
           <t>G | 398呎 (2房)
 $710万
 $17,841/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -25808,7 +25808,7 @@
           <t>J | 339呎 (2房)
 $670万
 $19,768/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -25816,7 +25816,7 @@
           <t>K | 339呎 (2房)
 $667万
 $19,675/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -25824,7 +25824,7 @@
           <t>L | 339呎 (2房)
 $660万
 $19,464/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -25832,7 +25832,7 @@
           <t>M | 339呎 (2房)
 $659万
 $19,453/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N24" s="21" t="inlineStr">
@@ -25840,7 +25840,7 @@
           <t>N | 339呎 (2房)
 $646万
 $19,064/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="O24" s="21" t="inlineStr">
@@ -25848,7 +25848,7 @@
           <t>P | 343呎 (2房)
 $651万
 $18,969/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="P24" s="21" t="inlineStr">
@@ -25856,7 +25856,7 @@
           <t>Q | 435呎 (2房)
 $899万
 $20,668/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -25871,7 +25871,7 @@
           <t>A | 642呎 (3房)
 $1187万
 $18,495/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -25879,7 +25879,7 @@
           <t>B | 390呎 (2房)
 $755万
 $19,362/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -25887,7 +25887,7 @@
           <t>C | 388呎 (2房)
 $746万
 $19,215/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -25895,7 +25895,7 @@
           <t>D | 389呎 (2房)
 $756万
 $19,432/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -25903,7 +25903,7 @@
           <t>E | 393呎 (2房)
 $698万
 $17,765/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -25911,7 +25911,7 @@
           <t>F | 399呎 (2房)
 $708万
 $17,748/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -25919,7 +25919,7 @@
           <t>G | 398呎 (2房)
 $709万
 $17,811/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -25935,7 +25935,7 @@
           <t>J | 339呎 (2房)
 $688万
 $20,301/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -25943,7 +25943,7 @@
           <t>K | 339呎 (2房)
 $649万
 $19,153/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -25951,7 +25951,7 @@
           <t>L | 339呎 (2房)
 $656万
 $19,365/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -25959,7 +25959,7 @@
           <t>M | 339呎 (2房)
 $656万
 $19,349/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
@@ -25967,7 +25967,7 @@
           <t>N | 339呎 (2房)
 $645万
 $19,035/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="O25" s="21" t="inlineStr">
@@ -25975,7 +25975,7 @@
           <t>P | 343呎 (2房)
 $647万
 $18,863/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="P25" s="21" t="inlineStr">
@@ -25983,7 +25983,7 @@
           <t>Q | 435呎 (2房)
 $848万
 $19,497/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -25998,7 +25998,7 @@
           <t>A | 642呎 (3房)
 $1185万
 $18,461/呎
-(26年-04月)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -26006,7 +26006,7 @@
           <t>B | 390呎 (2房)
 $752万
 $19,292/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -26014,7 +26014,7 @@
           <t>C | 388呎 (2房)
 $741万
 $19,089/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -26022,7 +26022,7 @@
           <t>D | 389呎 (2房)
 $735万
 $18,888/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -26030,7 +26030,7 @@
           <t>E | 393呎 (2房)
 $697万
 $17,734/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -26038,7 +26038,7 @@
           <t>F | 399呎 (2房)
 $707万
 $17,719/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -26046,7 +26046,7 @@
           <t>G | 398呎 (2房)
 $746万
 $18,756/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -26054,7 +26054,7 @@
           <t>H | 399呎 (2房)
 $698万
 $17,481/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -26062,7 +26062,7 @@
           <t>J | 339呎 (2房)
 $650万
 $19,169/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -26070,7 +26070,7 @@
           <t>K | 339呎 (2房)
 $661万
 $19,500/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -26078,7 +26078,7 @@
           <t>L | 339呎 (2房)
 $654万
 $19,292/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -26086,7 +26086,7 @@
           <t>M | 339呎 (2房)
 $654万
 $19,279/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N26" s="21" t="inlineStr">
@@ -26094,7 +26094,7 @@
           <t>N | 339呎 (2房)
 $643万
 $18,968/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="O26" s="21" t="inlineStr">
@@ -26102,7 +26102,7 @@
           <t>P | 343呎 (2房)
 $645万
 $18,797/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="P26" s="21" t="inlineStr">
@@ -26110,7 +26110,7 @@
           <t>Q | 435呎 (2房)
 $864万
 $19,853/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -26125,7 +26125,7 @@
           <t>A | 642呎 (3房)
 $1183万
 $18,427/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -26133,7 +26133,7 @@
           <t>B | 390呎 (2房)
 $751万
 $19,255/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -26141,7 +26141,7 @@
           <t>C | 388呎 (2房)
 $753万
 $19,415/呎
-(26年-04月)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -26149,7 +26149,7 @@
           <t>D | 389呎 (2房)
 $730万
 $18,764/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -26157,7 +26157,7 @@
           <t>E | 393呎 (2房)
 $696万
 $17,700/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -26165,7 +26165,7 @@
           <t>F | 399呎 (2房)
 $706万
 $17,684/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -26173,7 +26173,7 @@
           <t>G | 398呎 (2房)
 $703万
 $17,660/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -26181,7 +26181,7 @@
           <t>H | 399呎 (2房)
 $693万
 $17,365/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -26189,7 +26189,7 @@
           <t>J | 339呎 (2房)
 $678万
 $19,996/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -26197,7 +26197,7 @@
           <t>K | 339呎 (2房)
 $641万
 $18,919/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -26205,7 +26205,7 @@
           <t>L | 339呎 (2房)
 $648万
 $19,129/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -26213,7 +26213,7 @@
           <t>M | 339呎 (2房)
 $648万
 $19,115/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N27" s="21" t="inlineStr">
@@ -26221,7 +26221,7 @@
           <t>N | 339呎 (2房)
 $673万
 $19,854/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="O27" s="21" t="inlineStr">
@@ -26229,7 +26229,7 @@
           <t>P | 343呎 (2房)
 $657万
 $19,142/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="P27" s="21" t="inlineStr">
@@ -26237,7 +26237,7 @@
           <t>Q | 435呎 (2房)
 $842万
 $19,355/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -26316,7 +26316,7 @@
           <t>J | 301呎 (2房)
 $714万
 $23,708/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -26324,7 +26324,7 @@
           <t>K | 301呎 (2房)
 $715万
 $23,742/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -26332,7 +26332,7 @@
           <t>L | 301呎 (2房)
 $705万
 $23,424/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -26340,7 +26340,7 @@
           <t>M | 301呎 (2房)
 $690万
 $22,907/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N28" s="21" t="inlineStr">
@@ -26348,7 +26348,7 @@
           <t>N | 301呎 (2房)
 $687万
 $22,822/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="O28" s="21" t="inlineStr">
@@ -26356,7 +26356,7 @@
           <t>P | 306呎 (2房)
 $701万
 $22,922/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="P28" s="21" t="inlineStr">
@@ -26364,7 +26364,7 @@
           <t>Q | 435呎 (2房)
 $912万
 $20,956/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
